--- a/results/ate_summary_survey.xlsx
+++ b/results/ate_summary_survey.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3985398745276545</v>
+        <v>0.3985398745276548</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03933933271771811</v>
+        <v>0.03933933271771812</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3214361992250888</v>
+        <v>0.321436199225089</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4756435498302203</v>
+        <v>0.4756435498302205</v>
       </c>
       <c r="G2" t="n">
-        <v>4.032349524444153e-24</v>
+        <v>4.032349524444008e-24</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4677085962881629</v>
+        <v>0.4677085962881634</v>
       </c>
       <c r="I2" t="n">
-        <v>11.70361347220279</v>
+        <v>11.7036134722028</v>
       </c>
       <c r="J2" t="n">
         <v>3.778810823675779</v>
@@ -560,7 +560,7 @@
         <v>7095.308361203054</v>
       </c>
       <c r="N2" t="n">
-        <v>1.209704857333246e-23</v>
+        <v>1.209704857333202e-23</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0407159796972524</v>
+        <v>-0.04071597969725242</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -597,19 +597,19 @@
         <v>-0.1234163820460073</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04198442265150246</v>
+        <v>0.04198442265150243</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3345692469681958</v>
+        <v>0.3345692469681956</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.06413795733397941</v>
+        <v>-0.06413795733397988</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.874509212109811</v>
+        <v>-1.874509212109825</v>
       </c>
       <c r="J3" t="n">
-        <v>3.131806206400519</v>
+        <v>3.131806206400518</v>
       </c>
       <c r="K3" t="n">
         <v>3.191633673629502</v>
@@ -621,7 +621,7 @@
         <v>7093.805668076424</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3345692469681958</v>
+        <v>0.3345692469681956</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -648,16 +648,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04274619914367982</v>
+        <v>0.04274619914367981</v>
       </c>
       <c r="E4" t="n">
-        <v>0.146566195677793</v>
+        <v>0.1465661956777929</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3141282172729717</v>
+        <v>0.3141282172729716</v>
       </c>
       <c r="G4" t="n">
-        <v>7.096210791271728e-08</v>
+        <v>7.096210791271779e-08</v>
       </c>
       <c r="H4" t="n">
         <v>0.2528818070312245</v>
@@ -678,7 +678,7 @@
         <v>7093.528441237814</v>
       </c>
       <c r="N4" t="n">
-        <v>1.064431618690759e-07</v>
+        <v>1.064431618690767e-07</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>

--- a/results/ate_summary_survey.xlsx
+++ b/results/ate_summary_survey.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3642249454799705</v>
+        <v>0.3642249454799706</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -530,28 +530,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03859338896492541</v>
+        <v>0.03859338896492542</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2885832930673711</v>
+        <v>0.2885832930673712</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4398665978925698</v>
+        <v>0.43986659789257</v>
       </c>
       <c r="G2" t="n">
         <v>3.817947647451369e-21</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4385066466877225</v>
+        <v>0.4385066466877226</v>
       </c>
       <c r="I2" t="n">
-        <v>10.79210990728051</v>
+        <v>10.79210990728052</v>
       </c>
       <c r="J2" t="n">
-        <v>3.766054915857044</v>
+        <v>3.766054915857043</v>
       </c>
       <c r="K2" t="n">
-        <v>3.399208588958882</v>
+        <v>3.399208588958881</v>
       </c>
       <c r="L2" t="n">
         <v>6217</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.003320233432695046</v>
+        <v>-0.00332023343269494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -591,22 +591,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.05015882681790457</v>
+        <v>0.0501588268179046</v>
       </c>
       <c r="E3" t="n">
         <v>-0.1016297275025698</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0949892606371797</v>
+        <v>0.09498926063717988</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9472230553604767</v>
+        <v>0.9472230553604785</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0003080184020601404</v>
+        <v>-0.0003080184020606004</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.009354986623808818</v>
+        <v>-0.009354986623822791</v>
       </c>
       <c r="J3" t="n">
         <v>3.177946098060961</v>
@@ -618,10 +618,10 @@
         <v>6217</v>
       </c>
       <c r="M3" t="n">
-        <v>6055.852863629239</v>
+        <v>6055.85286362924</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9472230553604767</v>
+        <v>0.9472230553604785</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -651,19 +651,19 @@
         <v>0.04156356015237646</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08345569950857891</v>
+        <v>0.08345569950857894</v>
       </c>
       <c r="F4" t="n">
         <v>0.2463818614444229</v>
       </c>
       <c r="G4" t="n">
-        <v>7.251803917655306e-05</v>
+        <v>7.251803917655267e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1560165140786423</v>
+        <v>0.1560165140786419</v>
       </c>
       <c r="I4" t="n">
-        <v>5.32962131616578</v>
+        <v>5.329621316165764</v>
       </c>
       <c r="J4" t="n">
         <v>2.957435996302533</v>
@@ -678,7 +678,7 @@
         <v>6055.992193006093</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0001087770587648296</v>
+        <v>0.000108777058764829</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>

--- a/results/ate_summary_survey.xlsx
+++ b/results/ate_summary_survey.xlsx
@@ -530,28 +530,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03859338896492541</v>
+        <v>0.03859338896492542</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2885832930673712</v>
+        <v>0.2885832930673711</v>
       </c>
       <c r="F2" t="n">
         <v>0.4398665978925699</v>
       </c>
       <c r="G2" t="n">
-        <v>3.817947647451369e-21</v>
+        <v>3.817947647451479e-21</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4385066466877219</v>
+        <v>0.4385066466877242</v>
       </c>
       <c r="I2" t="n">
-        <v>10.7921099072805</v>
+        <v>10.79210990728055</v>
       </c>
       <c r="J2" t="n">
         <v>3.766054915857044</v>
       </c>
       <c r="K2" t="n">
-        <v>3.399208588958882</v>
+        <v>3.399208588958881</v>
       </c>
       <c r="L2" t="n">
         <v>6217</v>
@@ -560,7 +560,7 @@
         <v>6054.814949838281</v>
       </c>
       <c r="N2" t="n">
-        <v>1.145384294235411e-20</v>
+        <v>1.145384294235444e-20</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1649187804765008</v>
+        <v>0.1649187804765009</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -651,19 +651,19 @@
         <v>0.04156356015237647</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0834556995085788</v>
+        <v>0.08345569950857895</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2463818614444228</v>
+        <v>0.2463818614444229</v>
       </c>
       <c r="G4" t="n">
-        <v>7.251803917655401e-05</v>
+        <v>7.251803917655267e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1560165140786419</v>
+        <v>0.1560165140786423</v>
       </c>
       <c r="I4" t="n">
-        <v>5.329621316165764</v>
+        <v>5.32962131616578</v>
       </c>
       <c r="J4" t="n">
         <v>2.957435996302533</v>
@@ -675,10 +675,10 @@
         <v>6217</v>
       </c>
       <c r="M4" t="n">
-        <v>6055.992193006092</v>
+        <v>6055.992193006093</v>
       </c>
       <c r="N4" t="n">
-        <v>0.000108777058764831</v>
+        <v>0.000108777058764829</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>

--- a/results/ate_summary_survey.xlsx
+++ b/results/ate_summary_survey.xlsx
@@ -533,22 +533,22 @@
         <v>0.03859338896492542</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2885832930673711</v>
+        <v>0.2885832930673712</v>
       </c>
       <c r="F2" t="n">
         <v>0.4398665978925699</v>
       </c>
       <c r="G2" t="n">
-        <v>3.817947647451479e-21</v>
+        <v>3.817947647451369e-21</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4385066466877226</v>
+        <v>0.438506646687721</v>
       </c>
       <c r="I2" t="n">
-        <v>10.79210990728051</v>
+        <v>10.79210990728047</v>
       </c>
       <c r="J2" t="n">
-        <v>3.766054915857044</v>
+        <v>3.766054915857043</v>
       </c>
       <c r="K2" t="n">
         <v>3.399208588958882</v>
@@ -560,7 +560,7 @@
         <v>6054.814949838281</v>
       </c>
       <c r="N2" t="n">
-        <v>1.145384294235444e-20</v>
+        <v>1.145384294235411e-20</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.003320233432694951</v>
+        <v>-0.003320233432694986</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.05015882681790457</v>
+        <v>0.05015882681790459</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1016297275025697</v>
+        <v>-0.1016297275025698</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0949892606371798</v>
+        <v>0.09498926063717981</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9472230553604782</v>
+        <v>0.9472230553604777</v>
       </c>
       <c r="H3" t="n">
         <v>-0.0003080184020606005</v>
@@ -621,7 +621,7 @@
         <v>6055.852863629239</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9472230553604782</v>
+        <v>0.9472230553604777</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>

--- a/results/ate_summary_survey.xlsx
+++ b/results/ate_summary_survey.xlsx
@@ -539,16 +539,16 @@
         <v>0.4728684571825822</v>
       </c>
       <c r="G2" t="n">
-        <v>4.491231826565502e-25</v>
+        <v>4.491231826565693e-25</v>
       </c>
       <c r="H2" t="n">
         <v>0.473187209342842</v>
       </c>
       <c r="I2" t="n">
-        <v>11.74941746144692</v>
+        <v>11.74941746144691</v>
       </c>
       <c r="J2" t="n">
-        <v>3.798232017046068</v>
+        <v>3.798232017046069</v>
       </c>
       <c r="K2" t="n">
         <v>3.398883057584119</v>
@@ -560,7 +560,7 @@
         <v>5880.843365300834</v>
       </c>
       <c r="N2" t="n">
-        <v>1.347369547969651e-24</v>
+        <v>1.347369547969708e-24</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.008532607932754597</v>
+        <v>-0.008532607932754718</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -591,25 +591,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.0474334909408585</v>
+        <v>0.04743349094085851</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1015005418378442</v>
+        <v>-0.1015005418378443</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08443532597233498</v>
+        <v>0.08443532597233488</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8572422817678189</v>
+        <v>0.8572422817678169</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.00538806080623125</v>
+        <v>-0.005388060806230331</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.16363045856511</v>
+        <v>-0.1636304585650821</v>
       </c>
       <c r="J3" t="n">
-        <v>3.17353102488338</v>
+        <v>3.173531024883381</v>
       </c>
       <c r="K3" t="n">
         <v>3.178732399284887</v>
@@ -621,7 +621,7 @@
         <v>5880.506490622341</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8572422817678189</v>
+        <v>0.8572422817678169</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04545217693888522</v>
+        <v>0.0454521769388852</v>
       </c>
       <c r="E4" t="n">
         <v>0.08406118391107047</v>
@@ -657,16 +657,16 @@
         <v>0.2622304435493845</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001393008282982229</v>
+        <v>0.0001393008282982222</v>
       </c>
       <c r="H4" t="n">
-        <v>0.163544348696728</v>
+        <v>0.163544348696727</v>
       </c>
       <c r="I4" t="n">
-        <v>5.575640438035085</v>
+        <v>5.575640438035053</v>
       </c>
       <c r="J4" t="n">
-        <v>2.964674710289834</v>
+        <v>2.964674710289833</v>
       </c>
       <c r="K4" t="n">
         <v>2.80810487910786</v>
@@ -678,7 +678,7 @@
         <v>5880.104841727701</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0002089512424473344</v>
+        <v>0.0002089512424473333</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>

--- a/results/ate_summary_survey.xlsx
+++ b/results/ate_summary_survey.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3975380272033305</v>
+        <v>0.3975380272033306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -530,25 +530,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03843459909133462</v>
+        <v>0.03843459909133459</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3222075972240788</v>
+        <v>0.3222075972240789</v>
       </c>
       <c r="F2" t="n">
         <v>0.4728684571825823</v>
       </c>
       <c r="G2" t="n">
-        <v>4.491231826565693e-25</v>
+        <v>4.491231826565276e-25</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4731872093428421</v>
+        <v>0.4731872093428426</v>
       </c>
       <c r="I2" t="n">
-        <v>11.74941746144692</v>
+        <v>11.74941746144693</v>
       </c>
       <c r="J2" t="n">
-        <v>3.798232017046068</v>
+        <v>3.798232017046069</v>
       </c>
       <c r="K2" t="n">
         <v>3.398883057584119</v>
@@ -560,7 +560,7 @@
         <v>5880.843365300834</v>
       </c>
       <c r="N2" t="n">
-        <v>1.347369547969708e-24</v>
+        <v>1.347369547969583e-24</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.008532607932754689</v>
+        <v>-0.008532607932754567</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -591,22 +591,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.0474334909408585</v>
+        <v>0.04743349094085852</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1015005418378443</v>
+        <v>-0.1015005418378442</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08443532597233488</v>
+        <v>0.08443532597233505</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8572422817678174</v>
+        <v>0.8572422817678194</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.00538806080623125</v>
+        <v>-0.005388060806230791</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.16363045856511</v>
+        <v>-0.1636304585650961</v>
       </c>
       <c r="J3" t="n">
         <v>3.17353102488338</v>
@@ -621,7 +621,7 @@
         <v>5880.506490622341</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8572422817678174</v>
+        <v>0.8572422817678194</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -648,16 +648,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.0454521769388852</v>
+        <v>0.04545217693888521</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08406118391107047</v>
+        <v>0.08406118391107045</v>
       </c>
       <c r="F4" t="n">
         <v>0.2622304435493845</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001393008282982222</v>
+        <v>0.0001393008282982229</v>
       </c>
       <c r="H4" t="n">
         <v>0.163544348696728</v>
@@ -678,7 +678,7 @@
         <v>5880.104841727701</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0002089512424473333</v>
+        <v>0.0002089512424473344</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
